--- a/R Markdown/dados/Despesas_IDRGP_2024.xlsx
+++ b/R Markdown/dados/Despesas_IDRGP_2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cloudprodamazhotmail-my.sharepoint.com/personal/gabrielmachado_prefeitura_sp_gov_br/Documents/Área de Trabalho/IDRGP/IDRGP-2025/R Markdown/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A353B938-01B1-4473-A1D5-7F2E0CCFFCBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{A353B938-01B1-4473-A1D5-7F2E0CCFFCBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B260B7B-3A6D-4D3E-BFAE-852291220468}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9264" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="26" r:id="rId1"/>
@@ -574,7 +574,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -919,13 +919,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B88"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="44.28515625" customWidth="1"/>
     <col min="2" max="2" width="97.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -933,7 +933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -941,7 +941,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -949,7 +949,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -957,7 +957,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -965,7 +965,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -973,7 +973,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -981,7 +981,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -989,7 +989,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -997,7 +997,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1005,7 +1005,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -1013,7 +1013,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -1021,7 +1021,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -1029,7 +1029,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -1045,7 +1045,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -1053,7 +1053,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -1061,7 +1061,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -1069,7 +1069,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -1077,7 +1077,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -1085,7 +1085,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -1101,7 +1101,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>44</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>46</v>
       </c>
@@ -1117,7 +1117,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>48</v>
       </c>
@@ -1125,7 +1125,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>50</v>
       </c>
@@ -1133,7 +1133,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>52</v>
       </c>
@@ -1141,7 +1141,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>54</v>
       </c>
@@ -1149,7 +1149,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>56</v>
       </c>
@@ -1157,7 +1157,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>58</v>
       </c>
@@ -1165,7 +1165,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>60</v>
       </c>
@@ -1173,7 +1173,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>62</v>
       </c>
@@ -1181,7 +1181,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>64</v>
       </c>
@@ -1189,7 +1189,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>66</v>
       </c>
@@ -1197,7 +1197,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>68</v>
       </c>
@@ -1205,7 +1205,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>70</v>
       </c>
@@ -1213,7 +1213,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>72</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>74</v>
       </c>
@@ -1229,7 +1229,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>76</v>
       </c>
@@ -1237,7 +1237,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>78</v>
       </c>
@@ -1245,7 +1245,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>80</v>
       </c>
@@ -1253,7 +1253,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>82</v>
       </c>
@@ -1261,7 +1261,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>84</v>
       </c>
@@ -1269,7 +1269,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>86</v>
       </c>
@@ -1277,7 +1277,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>88</v>
       </c>
@@ -1285,7 +1285,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>90</v>
       </c>
@@ -1293,7 +1293,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>92</v>
       </c>
@@ -1301,7 +1301,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>94</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>96</v>
       </c>
@@ -1317,7 +1317,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>98</v>
       </c>
@@ -1325,7 +1325,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>100</v>
       </c>
@@ -1333,7 +1333,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>102</v>
       </c>
@@ -1341,7 +1341,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>104</v>
       </c>
@@ -1349,7 +1349,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>106</v>
       </c>
@@ -1357,7 +1357,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>108</v>
       </c>
@@ -1365,7 +1365,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>110</v>
       </c>
@@ -1373,7 +1373,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>112</v>
       </c>
@@ -1381,7 +1381,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>114</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>116</v>
       </c>
@@ -1397,7 +1397,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>118</v>
       </c>
@@ -1405,7 +1405,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>120</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>122</v>
       </c>
@@ -1421,7 +1421,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>124</v>
       </c>
@@ -1429,7 +1429,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>126</v>
       </c>
@@ -1437,7 +1437,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>128</v>
       </c>
@@ -1445,7 +1445,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>130</v>
       </c>
@@ -1453,7 +1453,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>132</v>
       </c>
@@ -1461,7 +1461,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>134</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>136</v>
       </c>
@@ -1477,7 +1477,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>138</v>
       </c>
@@ -1485,7 +1485,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>140</v>
       </c>
@@ -1493,7 +1493,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>142</v>
       </c>
@@ -1501,7 +1501,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>144</v>
       </c>
@@ -1509,7 +1509,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>146</v>
       </c>
@@ -1517,7 +1517,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>148</v>
       </c>
@@ -1525,7 +1525,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>150</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>152</v>
       </c>
@@ -1541,7 +1541,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>154</v>
       </c>
@@ -1549,7 +1549,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>156</v>
       </c>
@@ -1557,7 +1557,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>158</v>
       </c>
@@ -1565,7 +1565,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>160</v>
       </c>
@@ -1573,7 +1573,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>162</v>
       </c>
@@ -1581,7 +1581,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>164</v>
       </c>
@@ -1589,7 +1589,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>166</v>
       </c>
@@ -1597,7 +1597,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>168</v>
       </c>
@@ -1605,7 +1605,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>170</v>
       </c>
@@ -1613,7 +1613,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>172</v>
       </c>
@@ -1621,7 +1621,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>174</v>
       </c>
@@ -1640,26 +1640,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="40b0f00d-7fae-4e5d-a15a-83c0b7a3d872">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fdb686fa-97f2-457f-98c3-12ce29934077" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010035666C831EDD574A91CB44D07206055C" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ccdb995cebda962acd4b59e0915ff20d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40b0f00d-7fae-4e5d-a15a-83c0b7a3d872" xmlns:ns3="fdb686fa-97f2-457f-98c3-12ce29934077" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ef1a8544c33f55e4aa50ff441ccc834b" ns2:_="" ns3:_="">
     <xsd:import namespace="40b0f00d-7fae-4e5d-a15a-83c0b7a3d872"/>
@@ -1860,14 +1840,66 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="40b0f00d-7fae-4e5d-a15a-83c0b7a3d872">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fdb686fa-97f2-457f-98c3-12ce29934077" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A3A6EFF-2913-45FE-B994-11CF7C98A878}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A051219E-EAD3-4703-9BDE-8A5B39814273}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="40b0f00d-7fae-4e5d-a15a-83c0b7a3d872"/>
+    <ds:schemaRef ds:uri="fdb686fa-97f2-457f-98c3-12ce29934077"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB00E683-4D28-4FA2-B46A-A30D1AA700F4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB00E683-4D28-4FA2-B46A-A30D1AA700F4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A051219E-EAD3-4703-9BDE-8A5B39814273}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A3A6EFF-2913-45FE-B994-11CF7C98A878}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="40b0f00d-7fae-4e5d-a15a-83c0b7a3d872"/>
+    <ds:schemaRef ds:uri="fdb686fa-97f2-457f-98c3-12ce29934077"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{f398df9c-fd0c-4829-a003-c770a1c4a063}" enabled="0" method="" siteId="{f398df9c-fd0c-4829-a003-c770a1c4a063}" removed="1"/>
+</clbl:labelList>
 </file>
--- a/R Markdown/dados/Despesas_IDRGP_2024.xlsx
+++ b/R Markdown/dados/Despesas_IDRGP_2024.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cloudprodamazhotmail-my.sharepoint.com/personal/gabrielmachado_prefeitura_sp_gov_br/Documents/Área de Trabalho/IDRGP/IDRGP-2025/R Markdown/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{A353B938-01B1-4473-A1D5-7F2E0CCFFCBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B260B7B-3A6D-4D3E-BFAE-852291220468}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{A353B938-01B1-4473-A1D5-7F2E0CCFFCBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30ADDDAC-8280-49F0-A0FF-6CB834F89BAB}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3675" yWindow="3375" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="26" r:id="rId1"/>
@@ -40,13 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="176">
-  <si>
-    <t>Código_Ação</t>
-  </si>
-  <si>
-    <t>Ação</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="175">
   <si>
     <t>6245</t>
   </si>
@@ -54,9 +48,6 @@
     <t>Ações de Combate à Pobreza</t>
   </si>
   <si>
-    <t>6249</t>
-  </si>
-  <si>
     <t>Ações de Desenvolvimento Social</t>
   </si>
   <si>
@@ -568,6 +559,12 @@
   </si>
   <si>
     <t>Urbanização de Favelas</t>
+  </si>
+  <si>
+    <t>código_proj_ativ</t>
+  </si>
+  <si>
+    <t>descrição_proj_ativ</t>
   </si>
 </sst>
 </file>
@@ -927,706 +924,706 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>6249</v>
+      </c>
+      <c r="B3" t="s">
         <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B24" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B25" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B26" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B27" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B28" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B30" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B31" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B32" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B33" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B34" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B35" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B36" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B37" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B38" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B39" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B40" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B41" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B42" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B43" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B44" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B45" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B46" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B47" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B48" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B49" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B50" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B51" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B52" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B53" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B54" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B55" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B56" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B57" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B58" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B59" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B60" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B61" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B62" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B63" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B64" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B65" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B66" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B67" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B68" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B69" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B70" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B71" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B72" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B73" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B74" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B75" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B76" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B77" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B78" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B79" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B80" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B81" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B82" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B83" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B84" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B85" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B86" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B87" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B88" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -1841,15 +1838,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="40b0f00d-7fae-4e5d-a15a-83c0b7a3d872">
@@ -1858,6 +1846,15 @@
     <TaxCatchAll xmlns="fdb686fa-97f2-457f-98c3-12ce29934077" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1880,14 +1877,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB00E683-4D28-4FA2-B46A-A30D1AA700F4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A3A6EFF-2913-45FE-B994-11CF7C98A878}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -1898,6 +1887,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB00E683-4D28-4FA2-B46A-A30D1AA700F4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{f398df9c-fd0c-4829-a003-c770a1c4a063}" enabled="0" method="" siteId="{f398df9c-fd0c-4829-a003-c770a1c4a063}" removed="1"/>

--- a/R Markdown/dados/Despesas_IDRGP_2024.xlsx
+++ b/R Markdown/dados/Despesas_IDRGP_2024.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cloudprodamazhotmail-my.sharepoint.com/personal/gabrielmachado_prefeitura_sp_gov_br/Documents/Área de Trabalho/IDRGP/IDRGP-2025/R Markdown/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{A353B938-01B1-4473-A1D5-7F2E0CCFFCBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30ADDDAC-8280-49F0-A0FF-6CB834F89BAB}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{A353B938-01B1-4473-A1D5-7F2E0CCFFCBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04D22B39-9833-4900-81FB-5165D8195C66}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3375" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="26" r:id="rId1"/>
@@ -608,9 +608,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1210,11 +1211,11 @@
         <v>68</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+    <row r="37" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="2" t="s">
         <v>70</v>
       </c>
     </row>

--- a/R Markdown/dados/Despesas_IDRGP_2024.xlsx
+++ b/R Markdown/dados/Despesas_IDRGP_2024.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30117"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cloudprodamazhotmail-my.sharepoint.com/personal/gabrielmachado_prefeitura_sp_gov_br/Documents/Área de Trabalho/IDRGP/IDRGP-2025/R Markdown/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{A353B938-01B1-4473-A1D5-7F2E0CCFFCBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04D22B39-9833-4900-81FB-5165D8195C66}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{A353B938-01B1-4473-A1D5-7F2E0CCFFCBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61104B39-7BDB-44DA-A3B2-B8B8FEF0DE12}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,6 +42,12 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="175">
   <si>
+    <t>código_proj_ativ</t>
+  </si>
+  <si>
+    <t>descrição_proj_ativ</t>
+  </si>
+  <si>
     <t>6245</t>
   </si>
   <si>
@@ -559,19 +565,13 @@
   </si>
   <si>
     <t>Urbanização de Favelas</t>
-  </si>
-  <si>
-    <t>código_proj_ativ</t>
-  </si>
-  <si>
-    <t>descrição_proj_ativ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -611,7 +611,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -917,714 +917,714 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B88"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="44.28515625" customWidth="1"/>
     <col min="2" max="2" width="97.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="2">
+        <v>6249</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B30" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B31" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B33" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B35" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B36" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B37" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B38" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B39" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B40" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B41" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B42" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B43" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B44" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B45" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B46" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B47" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B48" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B49" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B50" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B51" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B52" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B53" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B54" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B55" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B56" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B57" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B58" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B59" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B60" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B61" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B62" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B63" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B64" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B65" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B66" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B67" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B68" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B69" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B70" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B71" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B72" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B73" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B74" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B75" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B76" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B77" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B78" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B79" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B80" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B81" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B82" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B83" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B84" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B85" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B86" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B87" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B88" t="s">
         <v>174</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>6249</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>33</v>
-      </c>
-      <c r="B19" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>39</v>
-      </c>
-      <c r="B22" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>41</v>
-      </c>
-      <c r="B23" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>45</v>
-      </c>
-      <c r="B25" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>47</v>
-      </c>
-      <c r="B26" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>49</v>
-      </c>
-      <c r="B27" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>51</v>
-      </c>
-      <c r="B28" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>53</v>
-      </c>
-      <c r="B29" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>55</v>
-      </c>
-      <c r="B30" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>57</v>
-      </c>
-      <c r="B31" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>59</v>
-      </c>
-      <c r="B32" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>61</v>
-      </c>
-      <c r="B33" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>63</v>
-      </c>
-      <c r="B34" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>65</v>
-      </c>
-      <c r="B35" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>67</v>
-      </c>
-      <c r="B36" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>71</v>
-      </c>
-      <c r="B38" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>73</v>
-      </c>
-      <c r="B39" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>75</v>
-      </c>
-      <c r="B40" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>77</v>
-      </c>
-      <c r="B41" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>79</v>
-      </c>
-      <c r="B42" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>81</v>
-      </c>
-      <c r="B43" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>83</v>
-      </c>
-      <c r="B44" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>85</v>
-      </c>
-      <c r="B45" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>87</v>
-      </c>
-      <c r="B46" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>89</v>
-      </c>
-      <c r="B47" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>91</v>
-      </c>
-      <c r="B48" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>93</v>
-      </c>
-      <c r="B49" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>95</v>
-      </c>
-      <c r="B50" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>97</v>
-      </c>
-      <c r="B51" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>99</v>
-      </c>
-      <c r="B52" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>101</v>
-      </c>
-      <c r="B53" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B54" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>105</v>
-      </c>
-      <c r="B55" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>107</v>
-      </c>
-      <c r="B56" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>109</v>
-      </c>
-      <c r="B57" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>111</v>
-      </c>
-      <c r="B58" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>113</v>
-      </c>
-      <c r="B59" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>115</v>
-      </c>
-      <c r="B60" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>117</v>
-      </c>
-      <c r="B61" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>119</v>
-      </c>
-      <c r="B62" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>121</v>
-      </c>
-      <c r="B63" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>123</v>
-      </c>
-      <c r="B64" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>125</v>
-      </c>
-      <c r="B65" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>127</v>
-      </c>
-      <c r="B66" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>129</v>
-      </c>
-      <c r="B67" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>131</v>
-      </c>
-      <c r="B68" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>133</v>
-      </c>
-      <c r="B69" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>135</v>
-      </c>
-      <c r="B70" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>137</v>
-      </c>
-      <c r="B71" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>139</v>
-      </c>
-      <c r="B72" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>141</v>
-      </c>
-      <c r="B73" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>143</v>
-      </c>
-      <c r="B74" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>145</v>
-      </c>
-      <c r="B75" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>147</v>
-      </c>
-      <c r="B76" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>149</v>
-      </c>
-      <c r="B77" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>151</v>
-      </c>
-      <c r="B78" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>153</v>
-      </c>
-      <c r="B79" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>155</v>
-      </c>
-      <c r="B80" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>157</v>
-      </c>
-      <c r="B81" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>159</v>
-      </c>
-      <c r="B82" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>161</v>
-      </c>
-      <c r="B83" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>163</v>
-      </c>
-      <c r="B84" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>165</v>
-      </c>
-      <c r="B85" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>167</v>
-      </c>
-      <c r="B86" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>169</v>
-      </c>
-      <c r="B87" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>171</v>
-      </c>
-      <c r="B88" t="s">
-        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -1638,6 +1638,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="40b0f00d-7fae-4e5d-a15a-83c0b7a3d872">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fdb686fa-97f2-457f-98c3-12ce29934077" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010035666C831EDD574A91CB44D07206055C" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ccdb995cebda962acd4b59e0915ff20d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40b0f00d-7fae-4e5d-a15a-83c0b7a3d872" xmlns:ns3="fdb686fa-97f2-457f-98c3-12ce29934077" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ef1a8544c33f55e4aa50ff441ccc834b" ns2:_="" ns3:_="">
     <xsd:import namespace="40b0f00d-7fae-4e5d-a15a-83c0b7a3d872"/>
@@ -1838,17 +1849,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="40b0f00d-7fae-4e5d-a15a-83c0b7a3d872">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fdb686fa-97f2-457f-98c3-12ce29934077" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1859,41 +1859,15 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A051219E-EAD3-4703-9BDE-8A5B39814273}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="40b0f00d-7fae-4e5d-a15a-83c0b7a3d872"/>
-    <ds:schemaRef ds:uri="fdb686fa-97f2-457f-98c3-12ce29934077"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A3A6EFF-2913-45FE-B994-11CF7C98A878}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A3A6EFF-2913-45FE-B994-11CF7C98A878}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="40b0f00d-7fae-4e5d-a15a-83c0b7a3d872"/>
-    <ds:schemaRef ds:uri="fdb686fa-97f2-457f-98c3-12ce29934077"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A051219E-EAD3-4703-9BDE-8A5B39814273}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB00E683-4D28-4FA2-B46A-A30D1AA700F4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB00E683-4D28-4FA2-B46A-A30D1AA700F4}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
